--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2B3D84-9943-4880-AC4B-DD0FF74C14CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DA2F66-2061-4EFA-B9F0-805A4FFDD1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>José Peñalba/Maryfer Higuera</t>
+  </si>
+  <si>
+    <t>José Peñalba</t>
+  </si>
+  <si>
+    <t>Maryfer Higuera</t>
   </si>
 </sst>
 </file>
@@ -380,7 +386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -733,6 +739,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="74.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
@@ -810,30 +817,32 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12" t="s">
-        <v>21</v>
+      <c r="D4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>9</v>
@@ -867,9 +876,11 @@
       <c r="H5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12" t="s">
-        <v>21</v>
+      <c r="I5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>19</v>
@@ -1088,9 +1099,11 @@
       <c r="H12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12" t="s">
-        <v>21</v>
+      <c r="I12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1115,9 +1128,11 @@
       <c r="H13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12" t="s">
-        <v>21</v>
+      <c r="I13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1142,9 +1157,11 @@
       <c r="H14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12" t="s">
-        <v>21</v>
+      <c r="I14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1169,9 +1186,11 @@
       <c r="H15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12" t="s">
-        <v>21</v>
+      <c r="I15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1196,9 +1215,11 @@
       <c r="H16" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12" t="s">
-        <v>21</v>
+      <c r="I16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1223,36 +1244,40 @@
       <c r="H17" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12" t="s">
-        <v>21</v>
+      <c r="I17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12" t="s">
-        <v>21</v>
+      <c r="D18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DA2F66-2061-4EFA-B9F0-805A4FFDD1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2628921-8B03-4810-BC9A-52133FA2DCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -374,9 +374,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -400,6 +397,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,35 +781,37 @@
       </c>
     </row>
     <row r="3" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12" t="s">
-        <v>21</v>
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>43</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -817,37 +819,37 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="11" t="s">
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>42</v>
       </c>
       <c r="O4" s="3" t="s">
@@ -855,37 +857,37 @@
       </c>
     </row>
     <row r="5" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="D5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>44</v>
       </c>
       <c r="O5" s="3" t="s">
@@ -893,37 +895,37 @@
       </c>
     </row>
     <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="D6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>45</v>
       </c>
       <c r="O6" s="3" t="s">
@@ -931,35 +933,35 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12" t="s">
+      <c r="D7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="s">
         <v>21</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>46</v>
       </c>
       <c r="O7" s="3" t="s">
@@ -967,478 +969,478 @@
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12" t="s">
+      <c r="D8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12" t="s">
+      <c r="D9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12" t="s">
+      <c r="D10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12" t="s">
+      <c r="D11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="D12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="11" t="s">
+      <c r="D13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="D14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="D15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="11" t="s">
+      <c r="D16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="11" t="s">
+      <c r="D17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="11" t="s">
+      <c r="D18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12" t="s">
+      <c r="D19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12" t="s">
+      <c r="D20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12" t="s">
+      <c r="D21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12" t="s">
+      <c r="D22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12" t="s">
+      <c r="D23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12" t="s">
+      <c r="D24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11" t="s">
         <v>21</v>
       </c>
     </row>

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2628921-8B03-4810-BC9A-52133FA2DCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87FEF15-3A36-430B-80CB-F67C16925957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -933,30 +933,32 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11" t="s">
-        <v>21</v>
+      <c r="D7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>25</v>

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87FEF15-3A36-430B-80CB-F67C16925957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD34FE2D-0FEA-453E-8956-CA22251F8949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -932,7 +933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>30</v>
       </c>
@@ -971,30 +972,32 @@
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11" t="s">
-        <v>21</v>
+      <c r="D8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD34FE2D-0FEA-453E-8956-CA22251F8949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0097C464-F126-4BD5-82F3-F56AA4CBF174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -1288,30 +1288,32 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11" t="s">
-        <v>21</v>
+      <c r="D19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0097C464-F126-4BD5-82F3-F56AA4CBF174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17E505A-F8A3-4E94-A72F-9642C076D677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -739,7 +739,10 @@
   <dimension ref="B2:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="74.109375" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1004,30 +1007,32 @@
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11" t="s">
-        <v>21</v>
+      <c r="D9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1317,30 +1322,32 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11" t="s">
-        <v>21</v>
+      <c r="D20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17E505A-F8A3-4E94-A72F-9642C076D677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B732857F-CA39-4263-9276-0CF8C4D2E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -376,9 +376,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -785,37 +782,37 @@
       </c>
     </row>
     <row r="3" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -823,37 +820,37 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5" t="s">
         <v>42</v>
       </c>
       <c r="O4" s="3" t="s">
@@ -861,37 +858,37 @@
       </c>
     </row>
     <row r="5" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="O5" s="3" t="s">
@@ -899,37 +896,37 @@
       </c>
     </row>
     <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="D6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="5" t="s">
         <v>45</v>
       </c>
       <c r="O6" s="3" t="s">
@@ -937,37 +934,37 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="D7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="O7" s="3" t="s">
@@ -975,378 +972,382 @@
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="D8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="J8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="D9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11" t="s">
-        <v>21</v>
+      <c r="D10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="s">
-        <v>21</v>
+      <c r="D11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="D13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="D14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="10" t="s">
+      <c r="D15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="D16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="10" t="s">
+      <c r="D17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="10" t="s">
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="D19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="D20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1354,26 +1355,26 @@
       <c r="B21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11" t="s">
+      <c r="D21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1381,26 +1382,26 @@
       <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11" t="s">
+      <c r="D22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1408,26 +1409,26 @@
       <c r="B23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11" t="s">
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1435,26 +1436,26 @@
       <c r="B24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11" t="s">
+      <c r="D24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10" t="s">
         <v>21</v>
       </c>
     </row>

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B732857F-CA39-4263-9276-0CF8C4D2E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6516052-0DDC-4FF3-BD7F-9504C1AA758F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="55">
   <si>
     <t>Challenge</t>
   </si>
@@ -1352,57 +1352,61 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10" t="s">
-        <v>21</v>
+      <c r="D21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10" t="s">
-        <v>21</v>
+      <c r="D22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1433,30 +1437,32 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10" t="s">
-        <v>21</v>
+      <c r="D24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Challenge Matrix.xlsx
+++ b/Documentation/Challenge Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\Space Dogs\International Projects\Global hack Week Agents\ghw-agents-2026\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6516052-0DDC-4FF3-BD7F-9504C1AA758F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D2518A-2367-431D-B5E2-F0DD85BA38A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A4E0EC1F-8485-4D74-B7FD-3A602CB8ED9A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
   <si>
     <t>Challenge</t>
   </si>
@@ -100,12 +100,6 @@
   </si>
   <si>
     <t>P2</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Not Submitt</t>
   </si>
   <si>
     <t>P3</t>
@@ -317,7 +311,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,12 +321,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -374,9 +362,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -391,9 +376,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -775,693 +757,695 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>43</v>
+      <c r="N3" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="D4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>42</v>
+      <c r="N4" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="D5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+    <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="9" t="s">
+      <c r="D18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="J19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="C20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
+      <c r="J22" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
+      <c r="C23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="D24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>11</v>
       </c>
     </row>
